--- a/risultati/matrice_confronti.xlsx
+++ b/risultati/matrice_confronti.xlsx
@@ -1154,7 +1154,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>5 run nella cella DP, 49 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
+          <t>6 run nella cella DP, 49 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">

--- a/risultati/matrice_confronti.xlsx
+++ b/risultati/matrice_confronti.xlsx
@@ -1092,7 +1092,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>5 run nella cella DP, 49 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
+          <t>6 run nella cella DP, 49 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">

--- a/risultati/matrice_confronti.xlsx
+++ b/risultati/matrice_confronti.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -968,7 +968,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>1 run nella cella DP, 49 nella cella no-DP; seed appaiabili: ['42']</t>
+          <t>6 run nella cella DP, 49 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=8.0</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=2.0</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>1 run nella cella DP, 49 nella cella no-DP; seed appaiabili: ['42']</t>
+          <t>5 run nella cella DP, 49 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=0.1</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=4.0</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>6 run nella cella DP, 49 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
+          <t>5 run nella cella DP, 49 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=0.5</t>
+          <t>dp_mode=dp-fedavg; no_dp=False; eps=8.0</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=1.0</t>
+          <t>dp_mode=local; no_dp=False; eps=0.1</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>11 run nella cella DP, 49 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
+          <t>6 run nella cella DP, 49 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -1243,122 +1243,246 @@
     <row r="13" ht="110" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>C-RQ2</t>
+          <t>C12</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>RQ2</t>
+          <t>RQ1</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>partizione IID</t>
+          <t>no-DP (regime naturale)</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>partizione non-IID (per sito)</t>
+          <t>dp_mode=local; no_dp=False; eps=0.5</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si, se appaiati per seed</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>dati, split, architettura, algoritmo, round, epoche, batch: identici</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>il braccio IID non esiste: i client sono i 3 siti reali raggruppati per site_id, quindi la partizione e' non-IID per natura, non per costruzione</t>
+          <t>nessuna differenza non controllata individuata oltre al fattore DP</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>nessuna configurazione registra split.strategy: default 'random' in tutte le 235 run; l'alternativa 'entity_aware' non e' mai stata attivata</t>
+          <t>6 run nella cella DP, 49 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>confronto non costruibile</t>
+          <t>da verificare: alcune celle contengono run di sweep diversi, e check_significance.py deduplica scegliendo il file piu' recente</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>confronto disponibile</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Serve costruire il riferimento IID rimescolando le sessioni fra i siti a parita' di numerosita' per client (guida Fase E).</t>
+          <t>Il contrasto B0/B2 della guida (sez. 8) e' questo. Manca invece il braccio B1 'clipping senza rumore', mai eseguito.</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>Fase A — lacuna rilevata (si esegue in Fase E)</t>
+          <t>Fase A — confrontabilita' (il confronto si esegue in Fase B)</t>
         </is>
       </c>
     </row>
     <row r="14" ht="110" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
+          <t>C13</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>RQ1</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>no-DP (regime naturale)</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>dp_mode=local; no_dp=False; eps=1.0</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>si, se appaiati per seed</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>dati, split, architettura, algoritmo, round, epoche, batch: identici</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>nessuna differenza non controllata individuata oltre al fattore DP</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>11 run nella cella DP, 49 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>da verificare: alcune celle contengono run di sweep diversi, e check_significance.py deduplica scegliendo il file piu' recente</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>confronto disponibile</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Il contrasto B0/B2 della guida (sez. 8) e' questo. Manca invece il braccio B1 'clipping senza rumore', mai eseguito.</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — confrontabilita' (il confronto si esegue in Fase B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="110" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>C-RQ2</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>RQ2</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>partizione IID</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>partizione non-IID (per sito)</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>il braccio IID non esiste: i client sono i 3 siti reali raggruppati per site_id, quindi la partizione e' non-IID per natura, non per costruzione</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>nessuna configurazione registra split.strategy: default 'random' in tutte le 235 run; l'alternativa 'entity_aware' non e' mai stata attivata</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>confronto non costruibile</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Serve costruire il riferimento IID rimescolando le sessioni fra i siti a parita' di numerosita' per client (guida Fase E).</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Fase A — lacuna rilevata (si esegue in Fase E)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="110" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
           <t>C-RQ3</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>RQ3</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>FedAvg (mu=0)</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>FedProx (mu=0.01)</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>il braccio mu=0 non esiste</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>proximal_mu = 0.01 su 235 run su 235, verificato con scripts/build_run_registry.py il 2026-09-21</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J14" s="5" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>confronto non costruibile</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
+      <c r="K16" s="3" t="inlineStr">
         <is>
           <t>Da eseguire da zero riusando split, candidati, checkpoint e condizioni DP della Fase B (guida Fase D).</t>
         </is>
       </c>
-      <c r="L14" s="3" t="inlineStr">
+      <c r="L16" s="3" t="inlineStr">
         <is>
           <t>Fase A — lacuna rilevata (si esegue in Fase D)</t>
         </is>

--- a/risultati/matrice_confronti.xlsx
+++ b/risultati/matrice_confronti.xlsx
@@ -1030,7 +1030,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>5 run nella cella DP, 49 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
+          <t>6 run nella cella DP, 49 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">

--- a/risultati/matrice_confronti.xlsx
+++ b/risultati/matrice_confronti.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=0.1</t>
+          <t>central, eps=0.1</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>5 run nella cella DP, 49 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
+          <t>5 run nella cella DP, 5 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>da verificare: alcune celle contengono run di sweep diversi, e check_significance.py deduplica scegliendo il file piu' recente</t>
+          <t>una run per seed, la piu' recente, con la regola di check_significance.py (segnalazioni 44, 45, 53); la cella puo' unire sweep diversi con lo stesso trattamento registrato</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=0.5</t>
+          <t>central, eps=0.5</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -658,12 +658,12 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>9 run nella cella DP, 49 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
+          <t>5 run nella cella DP, 5 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>da verificare: alcune celle contengono run di sweep diversi, e check_significance.py deduplica scegliendo il file piu' recente</t>
+          <t>una run per seed, la piu' recente, con la regola di check_significance.py (segnalazioni 44, 45, 53); la cella puo' unire sweep diversi con lo stesso trattamento registrato</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=central; no_dp=False; eps=1.0</t>
+          <t>central, eps=1.0</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>14 run nella cella DP, 49 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
+          <t>5 run nella cella DP, 5 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>da verificare: alcune celle contengono run di sweep diversi, e check_significance.py deduplica scegliendo il file piu' recente</t>
+          <t>una run per seed, la piu' recente, con la regola di check_significance.py (segnalazioni 44, 45, 53); la cella puo' unire sweep diversi con lo stesso trattamento registrato</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.1</t>
+          <t>dp-fedavg, eps=0.1</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>10 run nella cella DP, 49 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
+          <t>5 run nella cella DP, 5 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>da verificare: alcune celle contengono run di sweep diversi, e check_significance.py deduplica scegliendo il file piu' recente</t>
+          <t>una run per seed, la piu' recente, con la regola di check_significance.py (segnalazioni 44, 45, 53); la cella puo' unire sweep diversi con lo stesso trattamento registrato</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=0.5</t>
+          <t>dp-fedavg, eps=0.5</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>10 run nella cella DP, 49 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
+          <t>5 run nella cella DP, 5 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>da verificare: alcune celle contengono run di sweep diversi, e check_significance.py deduplica scegliendo il file piu' recente</t>
+          <t>una run per seed, la piu' recente, con la regola di check_significance.py (segnalazioni 44, 45, 53); la cella puo' unire sweep diversi con lo stesso trattamento registrato</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=1.0</t>
+          <t>dp-fedavg, eps=1.0</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>14 run nella cella DP, 49 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
+          <t>5 run nella cella DP, 5 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>da verificare: alcune celle contengono run di sweep diversi, e check_significance.py deduplica scegliendo il file piu' recente</t>
+          <t>una run per seed, la piu' recente, con la regola di check_significance.py (segnalazioni 44, 45, 53); la cella puo' unire sweep diversi con lo stesso trattamento registrato</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=16.0</t>
+          <t>dp-fedavg, eps=16.0</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -968,12 +968,12 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>6 run nella cella DP, 49 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
+          <t>5 run nella cella DP, 5 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>da verificare: alcune celle contengono run di sweep diversi, e check_significance.py deduplica scegliendo il file piu' recente</t>
+          <t>una run per seed, la piu' recente, con la regola di check_significance.py (segnalazioni 44, 45, 53); la cella puo' unire sweep diversi con lo stesso trattamento registrato</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=2.0</t>
+          <t>dp-fedavg, eps=2.0</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>6 run nella cella DP, 49 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
+          <t>5 run nella cella DP, 5 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>da verificare: alcune celle contengono run di sweep diversi, e check_significance.py deduplica scegliendo il file piu' recente</t>
+          <t>una run per seed, la piu' recente, con la regola di check_significance.py (segnalazioni 44, 45, 53); la cella puo' unire sweep diversi con lo stesso trattamento registrato</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=4.0</t>
+          <t>dp-fedavg, eps=4.0</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>5 run nella cella DP, 49 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
+          <t>5 run nella cella DP, 5 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>da verificare: alcune celle contengono run di sweep diversi, e check_significance.py deduplica scegliendo il file piu' recente</t>
+          <t>una run per seed, la piu' recente, con la regola di check_significance.py (segnalazioni 44, 45, 53); la cella puo' unire sweep diversi con lo stesso trattamento registrato</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=dp-fedavg; no_dp=False; eps=8.0</t>
+          <t>dp-fedavg, eps=8.0</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>6 run nella cella DP, 49 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
+          <t>5 run nella cella DP, 5 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>da verificare: alcune celle contengono run di sweep diversi, e check_significance.py deduplica scegliendo il file piu' recente</t>
+          <t>una run per seed, la piu' recente, con la regola di check_significance.py (segnalazioni 44, 45, 53); la cella puo' unire sweep diversi con lo stesso trattamento registrato</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=0.1</t>
+          <t>local, eps=0.1</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1216,12 +1216,12 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>6 run nella cella DP, 49 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
+          <t>5 run nella cella DP, 5 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>da verificare: alcune celle contengono run di sweep diversi, e check_significance.py deduplica scegliendo il file piu' recente</t>
+          <t>una run per seed, la piu' recente, con la regola di check_significance.py (segnalazioni 44, 45, 53); la cella puo' unire sweep diversi con lo stesso trattamento registrato</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=0.5</t>
+          <t>local, eps=0.5</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1278,12 +1278,12 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>6 run nella cella DP, 49 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
+          <t>5 run nella cella DP, 5 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>da verificare: alcune celle contengono run di sweep diversi, e check_significance.py deduplica scegliendo il file piu' recente</t>
+          <t>una run per seed, la piu' recente, con la regola di check_significance.py (segnalazioni 44, 45, 53); la cella puo' unire sweep diversi con lo stesso trattamento registrato</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>dp_mode=local; no_dp=False; eps=1.0</t>
+          <t>local, eps=1.0</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1340,12 +1340,12 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>11 run nella cella DP, 49 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
+          <t>5 run nella cella DP, 5 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>da verificare: alcune celle contengono run di sweep diversi, e check_significance.py deduplica scegliendo il file piu' recente</t>
+          <t>una run per seed, la piu' recente, con la regola di check_significance.py (segnalazioni 44, 45, 53); la cella puo' unire sweep diversi con lo stesso trattamento registrato</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>La guida (riga 152) chiede di segnalare le configurazioni duplicate: le celle central eps=0.5, central eps=1.0 e local eps=1.0 contengono piu' run per lo stesso seed, provenienti da sweep diversi.</t>
+          <t>La guida (riga 152) chiede di segnalare le configurazioni duplicate. Dal 2026-09-24 le celle hanno una run per seed, la piu' recente, con la regola di check_significance.py; i duplicati restano visibili nel registro run (segnalazioni 9 e 44).</t>
         </is>
       </c>
     </row>

--- a/risultati/matrice_confronti.xlsx
+++ b/risultati/matrice_confronti.xlsx
@@ -1382,47 +1382,47 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>partizione non-IID (per sito)</t>
+          <t>partizione per sito (non-IID)</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>si, appaiati per seed</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>dati, split globale, numerosita' per client, architettura, algoritmo, round, epoche, macchina e commit identici: cambia solo partition.strategy</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>il braccio IID non esiste: i client sono i 3 siti reali raggruppati per site_id, quindi la partizione e' non-IID per natura, non per costruzione</t>
+          <t>la partizione IID rompe corrispondenza client-sito, coerenza temporale e separazione fra utenti: e' un riferimento sperimentale, non un deployment</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>nessuna configurazione registra split.strategy: default 'random' in tutte le 235 run; l'alternativa 'entity_aware' non e' mai stata attivata</t>
+          <t>5 seed per braccio, senza DP, seconda macchina (experiments_altre_macchine/, commit 3815da7)</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>confronto non costruibile</t>
+          <t>una run per seed, la piu' recente</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>confronto disponibile</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Serve costruire il riferimento IID rimescolando le sessioni fra i siti a parita' di numerosita' per client (guida Fase E).</t>
+          <t>Numeri nel foglio RQ2_partizione di Matrice_sintesi.xlsx. Manca il braccio con DP: stessa coppia al punto operativo client-level.</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>Fase A — lacuna rilevata (si esegue in Fase E)</t>
+          <t>Fase E — braccio senza DP eseguito, braccio con DP da eseguire</t>
         </is>
       </c>
     </row>

--- a/risultati/matrice_confronti.xlsx
+++ b/risultati/matrice_confronti.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>dp-fedavg, eps=8.0</t>
+          <t>dp-fedavg, eps=64.0</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>local, eps=0.1</t>
+          <t>dp-fedavg, eps=8.0</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>local, eps=0.5</t>
+          <t>local, eps=0.1</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>local, eps=1.0</t>
+          <t>local, eps=0.5</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1367,47 +1367,47 @@
     <row r="15" ht="110" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>C-RQ2</t>
+          <t>C14</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>RQ2</t>
+          <t>RQ1</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>partizione IID</t>
+          <t>no-DP (regime naturale)</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>partizione per sito (non-IID)</t>
+          <t>local, eps=1.0</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>si, appaiati per seed</t>
+          <t>si, se appaiati per seed</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>dati, split globale, numerosita' per client, architettura, algoritmo, round, epoche, macchina e commit identici: cambia solo partition.strategy</t>
+          <t>dati, split, architettura, algoritmo, round, epoche, batch: identici</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>la partizione IID rompe corrispondenza client-sito, coerenza temporale e separazione fra utenti: e' un riferimento sperimentale, non un deployment</t>
+          <t>nessuna differenza non controllata individuata oltre al fattore DP</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>5 seed per braccio, senza DP, seconda macchina (experiments_altre_macchine/, commit 3815da7)</t>
+          <t>5 run nella cella DP, 5 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>una run per seed, la piu' recente</t>
+          <t>una run per seed, la piu' recente, con la regola di check_significance.py (segnalazioni 44, 45, 53); la cella puo' unire sweep diversi con lo stesso trattamento registrato</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1417,72 +1417,134 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Numeri nel foglio RQ2_partizione di Matrice_sintesi.xlsx. Manca il braccio con DP: stessa coppia al punto operativo client-level.</t>
+          <t>Il contrasto B0/B2 della guida (sez. 8) e' questo. Manca invece il braccio B1 'clipping senza rumore', mai eseguito.</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>Fase E — braccio senza DP eseguito, braccio con DP da eseguire</t>
+          <t>Fase A — confrontabilita' (il confronto si esegue in Fase B)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="110" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>C-RQ2</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>RQ2</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>partizione IID</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>partizione per sito (non-IID)</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>si, appaiati per seed</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>dati, split globale, numerosita' per client, architettura, algoritmo, round, epoche, macchina e commit identici: cambia solo partition.strategy</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>la partizione IID rompe corrispondenza client-sito, coerenza temporale e separazione fra utenti: e' un riferimento sperimentale, non un deployment</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>5 seed per braccio, senza DP, seconda macchina (experiments_altre_macchine/, commit 3815da7)</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>una run per seed, la piu' recente</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>confronto disponibile</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Numeri nel foglio RQ2_partizione di Matrice_sintesi.xlsx. Manca il braccio con DP: stessa coppia al punto operativo client-level.</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Fase E — braccio senza DP eseguito, braccio con DP da eseguire</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="110" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
           <t>C-RQ3</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>RQ3</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>FedAvg (mu=0)</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>FedProx (mu=0.01)</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>il braccio mu=0 non esiste</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>proximal_mu = 0.01 su 235 run su 235, verificato con scripts/build_run_registry.py il 2026-09-21</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>confronto non costruibile</t>
         </is>
       </c>
-      <c r="K16" s="3" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>Da eseguire da zero riusando split, candidati, checkpoint e condizioni DP della Fase B (guida Fase D).</t>
         </is>
       </c>
-      <c r="L16" s="3" t="inlineStr">
+      <c r="L17" s="3" t="inlineStr">
         <is>
           <t>Fase A — lacuna rilevata (si esegue in Fase D)</t>
         </is>

--- a/risultati/matrice_confronti.xlsx
+++ b/risultati/matrice_confronti.xlsx
@@ -1479,12 +1479,12 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Numeri nel foglio RQ2_partizione di Matrice_sintesi.xlsx. Manca il braccio con DP: stessa coppia al punto operativo client-level.</t>
+          <t>Numeri nel foglio RQ2_partizione di Matrice_sintesi.xlsx. Braccio con DP (eps = 64, C = 1) eseguito sulla stessa macchina.</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>Fase E — braccio senza DP eseguito, braccio con DP da eseguire</t>
+          <t>Fase E — bracci senza DP e con DP eseguiti</t>
         </is>
       </c>
     </row>

--- a/risultati/matrice_confronti.xlsx
+++ b/risultati/matrice_confronti.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1429,47 +1429,47 @@
     <row r="16" ht="110" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>C-RQ2</t>
+          <t>C15</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>RQ2</t>
+          <t>RQ1</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>partizione IID</t>
+          <t>no-DP (regime naturale)</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>partizione per sito (non-IID)</t>
+          <t>record-DP, nm=1.0</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>si, appaiati per seed</t>
+          <t>si, se appaiati per seed</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>dati, split globale, numerosita' per client, architettura, algoritmo, round, epoche, macchina e commit identici: cambia solo partition.strategy</t>
+          <t>dati, split, algoritmo, round, epoche, batch: identici; l'architettura no (GroupNorm al posto di BatchNorm, segnalazione 49)</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>la partizione IID rompe corrispondenza client-sito, coerenza temporale e separazione fra utenti: e' un riferimento sperimentale, non un deployment</t>
+          <t>normalizzazione GroupNorm e clipping per esempio: il rapporto sul no-DP mescola rumore e architettura finche' manca una cella no-DP con GroupNorm; unita' protetta record, da confrontare col client-level a costo comparabile, non allo stesso eps (ESPERIMENTI.md, E-B)</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>5 seed per braccio, senza DP, seconda macchina (experiments_altre_macchine/, commit 3815da7)</t>
+          <t>5 run nella cella DP, 5 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>una run per seed, la piu' recente</t>
+          <t>una run per seed, la piu' recente, con la regola di check_significance.py (segnalazioni 44, 45, 53); la cella puo' unire sweep diversi con lo stesso trattamento registrato</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1479,72 +1479,134 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Numeri nel foglio RQ2_partizione di Matrice_sintesi.xlsx. Braccio con DP (eps = 64, C = 1) eseguito sulla stessa macchina.</t>
+          <t>Il contrasto B0/B2 della guida (sez. 8) e' questo. Manca invece il braccio B1 'clipping senza rumore', mai eseguito.</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>Fase E — bracci senza DP e con DP eseguiti</t>
+          <t>Fase A — confrontabilita' (il confronto si esegue in Fase B)</t>
         </is>
       </c>
     </row>
     <row r="17" ht="110" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
+          <t>C-RQ2</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>RQ2</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>partizione IID</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>partizione per sito (non-IID)</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>si, appaiati per seed</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>dati, split globale, numerosita' per client, architettura, algoritmo, round, epoche, macchina e commit identici: cambia solo partition.strategy</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>la partizione IID rompe corrispondenza client-sito, coerenza temporale e separazione fra utenti: e' un riferimento sperimentale, non un deployment</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>5 seed per braccio, senza DP, seconda macchina (experiments_altre_macchine/, commit 3815da7)</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>una run per seed, la piu' recente</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>confronto disponibile</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Numeri nel foglio RQ2_partizione di Matrice_sintesi.xlsx. Braccio con DP (eps = 64, C = 1) eseguito sulla stessa macchina.</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Fase E — bracci senza DP e con DP eseguiti</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="110" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
           <t>C-RQ3</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>RQ3</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>FedAvg (mu=0)</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>FedProx (mu=0.01)</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>il braccio mu=0 non esiste</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>proximal_mu = 0.01 su 235 run su 235, verificato con scripts/build_run_registry.py il 2026-09-21</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>il braccio mu=0 non e' in questo checkout (E-E gira su un'altra macchina e andra' in experiments_altre_macchine/)</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>algoritmo registrato nel registro run: FedProx, mu=0.01: 300</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>confronto non costruibile</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="K18" s="3" t="inlineStr">
         <is>
           <t>Da eseguire da zero riusando split, candidati, checkpoint e condizioni DP della Fase B (guida Fase D).</t>
         </is>
       </c>
-      <c r="L17" s="3" t="inlineStr">
+      <c r="L18" s="3" t="inlineStr">
         <is>
           <t>Fase A — lacuna rilevata (si esegue in Fase D)</t>
         </is>

--- a/risultati/matrice_confronti.xlsx
+++ b/risultati/matrice_confronti.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1491,47 +1491,47 @@
     <row r="17" ht="110" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>C-RQ2</t>
+          <t>C16</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>RQ2</t>
+          <t>RQ1</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>partizione IID</t>
+          <t>no-DP (regime naturale)</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>partizione per sito (non-IID)</t>
+          <t>record-DP, nm=2.0</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>si, appaiati per seed</t>
+          <t>si, se appaiati per seed</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>dati, split globale, numerosita' per client, architettura, algoritmo, round, epoche, macchina e commit identici: cambia solo partition.strategy</t>
+          <t>dati, split, algoritmo, round, epoche, batch: identici; l'architettura no (GroupNorm al posto di BatchNorm, segnalazione 49)</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>la partizione IID rompe corrispondenza client-sito, coerenza temporale e separazione fra utenti: e' un riferimento sperimentale, non un deployment</t>
+          <t>normalizzazione GroupNorm e clipping per esempio: il rapporto sul no-DP mescola rumore e architettura finche' manca una cella no-DP con GroupNorm; unita' protetta record, da confrontare col client-level a costo comparabile, non allo stesso eps (ESPERIMENTI.md, E-B)</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>5 seed per braccio, senza DP, seconda macchina (experiments_altre_macchine/, commit 3815da7)</t>
+          <t>3 run nella cella DP, 5 nella cella no-DP; seed appaiabili: ['123', '42', '456']</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>una run per seed, la piu' recente</t>
+          <t>una run per seed, la piu' recente, con la regola di check_significance.py (segnalazioni 44, 45, 53); la cella puo' unire sweep diversi con lo stesso trattamento registrato</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1541,74 +1541,136 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Numeri nel foglio RQ2_partizione di Matrice_sintesi.xlsx. Braccio con DP (eps = 64, C = 1) eseguito sulla stessa macchina.</t>
+          <t>Il contrasto B0/B2 della guida (sez. 8) e' questo. Manca invece il braccio B1 'clipping senza rumore', mai eseguito.</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>Fase E — bracci senza DP e con DP eseguiti</t>
+          <t>Fase A — confrontabilita' (il confronto si esegue in Fase B)</t>
         </is>
       </c>
     </row>
     <row r="18" ht="110" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
+          <t>C-RQ2</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>RQ2</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>partizione IID</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>partizione per sito (non-IID)</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>si, appaiati per seed</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>dati, split globale, numerosita' per client, architettura, algoritmo, round, epoche, macchina e commit identici: cambia solo partition.strategy</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>la partizione IID rompe corrispondenza client-sito, coerenza temporale e separazione fra utenti: e' un riferimento sperimentale, non un deployment</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>5 seed per braccio, senza DP, seconda macchina (experiments_altre_macchine/, commit 3815da7)</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>una run per seed, la piu' recente</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>confronto disponibile</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Numeri nel foglio RQ2_partizione di Matrice_sintesi.xlsx. Braccio con DP (eps = 64, C = 1) eseguito sulla stessa macchina.</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Fase E — bracci senza DP e con DP eseguiti</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="110" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
           <t>C-RQ3</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>RQ3</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>FedAvg (mu=0)</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>FedProx (mu=0.01)</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>il braccio mu=0 non e' in questo checkout (E-E gira su un'altra macchina e andra' in experiments_altre_macchine/)</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>algoritmo registrato nel registro run: FedProx, mu=0.01: 300</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>confronto non costruibile</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>Da eseguire da zero riusando split, candidati, checkpoint e condizioni DP della Fase B (guida Fase D).</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>Fase A — lacuna rilevata (si esegue in Fase D)</t>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>si, appaiati per seed</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>dati, split, partizione, architettura, round, epoche, macchina e commit identici: cambia solo ml.proximal_mu</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>i due bracci senza DP hanno girato in parallelo sulla stessa macchina; la loss di addestramento locale di FedProx include il termine prossimale (segnalazione 59)</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>5 seed per braccio, senza DP, terza macchina (experiments_altre_macchine/, commit 478d471)</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>una run per seed, la piu' recente</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>confronto disponibile</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Numeri nel foglio RQ3_algoritmo di Matrice_sintesi.xlsx. Loss sull'holdout FedAvg contro FedProx 0.000397 contro 0.001564 (t = -6.63). Braccio con DP (eps = 64, C = 1) in corso o da eseguire.</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Fase D — braccio senza DP eseguito</t>
         </is>
       </c>
     </row>

--- a/risultati/matrice_confronti.xlsx
+++ b/risultati/matrice_confronti.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>record-DP, nm=1.0</t>
+          <t>no-DP baseline, norm=group</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>normalizzazione GroupNorm e clipping per esempio: il rapporto sul no-DP mescola rumore e architettura finche' manca una cella no-DP con GroupNorm; unita' protetta record, da confrontare col client-level a costo comparabile, non allo stesso eps (ESPERIMENTI.md, E-B)</t>
+          <t>nessuna differenza non controllata individuata oltre al fattore DP</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Il contrasto B0/B2 della guida (sez. 8) e' questo. Manca invece il braccio B1 'clipping senza rumore', mai eseguito.</t>
+          <t>Nessuna DP: e' il riferimento con la normalizzazione delle celle record-DP (E-B), non un contrasto della guida.</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>record-DP, nm=2.0</t>
+          <t>record-DP, nm=1.0</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>3 run nella cella DP, 5 nella cella no-DP; seed appaiabili: ['123', '42', '456']</t>
+          <t>5 run nella cella DP, 5 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -1553,47 +1553,47 @@
     <row r="18" ht="110" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>C-RQ2</t>
+          <t>C17</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>RQ2</t>
+          <t>RQ1</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>partizione IID</t>
+          <t>no-DP (regime naturale)</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>partizione per sito (non-IID)</t>
+          <t>record-DP, nm=2.0</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>si, appaiati per seed</t>
+          <t>si, se appaiati per seed</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>dati, split globale, numerosita' per client, architettura, algoritmo, round, epoche, macchina e commit identici: cambia solo partition.strategy</t>
+          <t>dati, split, algoritmo, round, epoche, batch: identici; l'architettura no (GroupNorm al posto di BatchNorm, segnalazione 49)</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>la partizione IID rompe corrispondenza client-sito, coerenza temporale e separazione fra utenti: e' un riferimento sperimentale, non un deployment</t>
+          <t>normalizzazione GroupNorm e clipping per esempio: il rapporto sul no-DP mescola rumore e architettura finche' manca una cella no-DP con GroupNorm; unita' protetta record, da confrontare col client-level a costo comparabile, non allo stesso eps (ESPERIMENTI.md, E-B)</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>5 seed per braccio, senza DP, seconda macchina (experiments_altre_macchine/, commit 3815da7)</t>
+          <t>5 run nella cella DP, 5 nella cella no-DP; seed appaiabili: ['123', '1234', '42', '456', '789']</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>una run per seed, la piu' recente</t>
+          <t>una run per seed, la piu' recente, con la regola di check_significance.py (segnalazioni 44, 45, 53); la cella puo' unire sweep diversi con lo stesso trattamento registrato</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1603,72 +1603,134 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Numeri nel foglio RQ2_partizione di Matrice_sintesi.xlsx. Braccio con DP (eps = 64, C = 1) eseguito sulla stessa macchina.</t>
+          <t>Il contrasto B0/B2 della guida (sez. 8) e' questo. Manca invece il braccio B1 'clipping senza rumore', mai eseguito.</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>Fase E — bracci senza DP e con DP eseguiti</t>
+          <t>Fase A — confrontabilita' (il confronto si esegue in Fase B)</t>
         </is>
       </c>
     </row>
     <row r="19" ht="110" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
+          <t>C-RQ2</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>RQ2</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>partizione IID</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>partizione per sito (non-IID)</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>si, appaiati per seed</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>dati, split globale, numerosita' per client, architettura, algoritmo, round, epoche, macchina e commit identici: cambia solo partition.strategy</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>la partizione IID rompe corrispondenza client-sito, coerenza temporale e separazione fra utenti: e' un riferimento sperimentale, non un deployment</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>5 seed per braccio, senza DP, seconda macchina (experiments_altre_macchine/, commit 3815da7)</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>una run per seed, la piu' recente</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>confronto disponibile</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Numeri nel foglio RQ2_partizione di Matrice_sintesi.xlsx. Braccio con DP (eps = 64, C = 1) eseguito sulla stessa macchina.</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Fase E — bracci senza DP e con DP eseguiti</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="110" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
           <t>C-RQ3</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>RQ3</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>FedAvg (mu=0)</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>FedProx (mu=0.01)</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>si, appaiati per seed</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>dati, split, partizione, architettura, round, epoche, macchina e commit identici: cambia solo ml.proximal_mu</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>i due bracci senza DP hanno girato in parallelo sulla stessa macchina; la loss di addestramento locale di FedProx include il termine prossimale (segnalazione 59)</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>5 seed per braccio, senza DP, terza macchina (experiments_altre_macchine/, commit 478d471)</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>una run per seed, la piu' recente</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>confronto disponibile</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>confronto disponibile</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
         <is>
           <t>Numeri nel foglio RQ3_algoritmo di Matrice_sintesi.xlsx. Loss sull'holdout FedAvg contro FedProx 0.000397 contro 0.001564 (t = -6.63). Braccio con DP (eps = 64, C = 1) in corso o da eseguire.</t>
         </is>
       </c>
-      <c r="L19" s="3" t="inlineStr">
+      <c r="L20" s="3" t="inlineStr">
         <is>
           <t>Fase D — braccio senza DP eseguito</t>
         </is>
